--- a/data/trans_camb/P32B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Edad-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,59; 7,53</t>
+          <t>1,63; 7,84</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,89; 3,79</t>
+          <t>-0,99; 3,8</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,31; -0,12</t>
+          <t>-3,43; -0,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,52; 3,97</t>
+          <t>-2,8; 3,95</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,75; 2,41</t>
+          <t>-3,63; 2,46</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,28; 11,19</t>
+          <t>-2,06; 11,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,81; 4,93</t>
+          <t>0,46; 4,91</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,29; 2,57</t>
+          <t>-1,1; 2,55</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,77; 3,4</t>
+          <t>-1,81; 3,03</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>12,17; 1783,27</t>
+          <t>11,64; 1962,02</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-68,33; 1004,93</t>
+          <t>-66,95; 992,08</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-73,42; 504,66</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,5; 722,0</t>
+          <t>13,83; 585,49</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-57,72; 338,19</t>
+          <t>-56,14; 388,7</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-93,72; 423,35</t>
+          <t>-95,82; 419,58</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,52</t>
+          <t>0,96; 4,63</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,16</t>
+          <t>1,25; 5,2</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,75</t>
+          <t>0,86; 9,71</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-2,3; 1,17</t>
+          <t>-1,91; 1,15</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,0; 3,69</t>
+          <t>-0,79; 3,39</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,34</t>
+          <t>-1,91; 1,81</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,45; 3,05</t>
+          <t>0,46; 3,15</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,85; 3,84</t>
+          <t>0,84; 3,74</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,76</t>
+          <t>0,36; 5,5</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>35,97; 2487,15</t>
+          <t>37,52; 2471,53</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>78,87; —</t>
+          <t>51,51; 2336,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>15,69; —</t>
+          <t>-23,96; —</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>16,3; 1076,98</t>
+          <t>21,5; 1163,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>56,96; 1723,96</t>
+          <t>48,69; 1390,2</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,5; 1950,08</t>
+          <t>-3,93; 1475,99</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,83; 4,57</t>
+          <t>0,91; 4,37</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,91</t>
+          <t>0,17; 3,03</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,48; 2,1</t>
+          <t>-0,55; 2,24</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,4; 0,8</t>
+          <t>-1,45; 0,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,14; 1,52</t>
+          <t>-1,34; 1,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,5; 2,9</t>
+          <t>-0,55; 2,99</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,52; 3,04</t>
+          <t>0,48; 2,93</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,04; 2,11</t>
+          <t>-0,04; 2,02</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,94</t>
+          <t>-0,26; 1,75</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>28,69; —</t>
+          <t>11,64; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-52,69; —</t>
+          <t>-43,72; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>13,33; 1602,91</t>
+          <t>5,4; 1636,54</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-18,8; —</t>
+          <t>-33,08; 1190,11</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-62,85; 1296,88</t>
+          <t>-68,31; —</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,53; 3,26</t>
+          <t>0,54; 3,18</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,98; 4,71</t>
+          <t>0,95; 4,47</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 2,81</t>
+          <t>0,3; 2,82</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 0,0</t>
+          <t>-4,0; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,43; 1,68</t>
+          <t>-2,38; 1,68</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,25; 1,9</t>
+          <t>-2,24; 1,85</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,08; 1,93</t>
+          <t>-0,18; 1,81</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,38; 2,89</t>
+          <t>0,39; 2,97</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>0,05; 2,15</t>
+          <t>-0,05; 1,97</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,57; 1,79</t>
+          <t>-5,09; 1,77</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,18</t>
+          <t>-5,66; 1,03</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-4,44; 3,05</t>
+          <t>-3,93; 3,07</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,0</t>
+          <t>-8,14; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,91; 0,0</t>
+          <t>-6,26; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,66; 3,86</t>
+          <t>-3,57; 3,79</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,33; 0,78</t>
+          <t>-4,67; 0,69</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,64; 0,24</t>
+          <t>-4,77; 0,55</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,66; 2,75</t>
+          <t>-2,87; 2,63</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-95,58; 225,68</t>
+          <t>-100,0; 218,46</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-93,42; 116,16</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-69,49; 212,6</t>
+          <t>-66,55; 191,17</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-97,43; 80,38</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-93,5; 51,77</t>
+          <t>-94,89; 65,38</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-54,06; 211,54</t>
+          <t>-58,58; 194,86</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,64; 7,71</t>
+          <t>0,63; 7,66</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,75</t>
+          <t>0,0; 2,74</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,51; 3,58</t>
+          <t>0,36; 3,17</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,26</t>
+          <t>0,0; 1,22</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,45; 5,64</t>
+          <t>0,47; 6,18</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,62</t>
+          <t>0,0; 2,49</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,07; 1,66</t>
+          <t>0,08; 1,61</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 9,2</t>
+          <t>-2,72; 10,41</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,33; 1,66</t>
+          <t>-5,45; 1,71</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,12; 2,93</t>
+          <t>-4,45; 2,98</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 8,18</t>
+          <t>0,0; 7,6</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,22; 9,88</t>
+          <t>-2,27; 8,24</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,57; 1,22</t>
+          <t>-4,48; 1,22</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,25; 2,73</t>
+          <t>-3,04; 2,94</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,13; 2,86</t>
+          <t>1,2; 3,04</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,57; 2,09</t>
+          <t>0,51; 2,12</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,36; 2,13</t>
+          <t>0,33; 2,17</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 0,4</t>
+          <t>-1,23; 0,44</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,83</t>
+          <t>-0,92; 0,86</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,8; 1,39</t>
+          <t>-0,82; 1,36</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,63; 1,96</t>
+          <t>0,59; 1,88</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,27; 1,4</t>
+          <t>0,23; 1,42</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,11; 1,57</t>
+          <t>0,08; 1,54</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>91,38; 537,71</t>
+          <t>92,96; 543,63</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>40,23; 377,81</t>
+          <t>38,4; 393,79</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>21,08; 381,53</t>
+          <t>20,03; 366,01</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-81,27; 79,7</t>
+          <t>-78,24; 100,15</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-63,65; 154,89</t>
+          <t>-61,33; 169,78</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-50,68; 231,18</t>
+          <t>-52,38; 214,67</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>46,47; 284,25</t>
+          <t>48,87; 288,83</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>17,34; 215,81</t>
+          <t>16,6; 224,96</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,11; 233,72</t>
+          <t>5,96; 229,3</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P32B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P32B-Edad-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-1,12</t>
+          <t>-0,22</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,79</t>
+          <t>3,29</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-0,06</t>
+          <t>1,21</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>1,63; 7,84</t>
+          <t>1,28; 7,11</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 3,8</t>
+          <t>-0,96; 3,94</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,43; -0,18</t>
+          <t>-2,1; 3,18</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-2,8; 3,95</t>
+          <t>-2,32; 3,97</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-3,63; 2,46</t>
+          <t>-3,32; 2,42</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,06; 11,05</t>
+          <t>-1,36; 12,91</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,46; 4,91</t>
+          <t>0,8; 5,13</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-1,1; 2,55</t>
+          <t>-1,24; 2,46</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-1,81; 3,03</t>
+          <t>-1,07; 4,96</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-92,0%</t>
+          <t>-17,97%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>81,94%</t>
+          <t>151,08%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-3,76%</t>
+          <t>75,52%</t>
         </is>
       </c>
     </row>
@@ -783,12 +783,12 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,64; 1962,02</t>
+          <t>20,25; 1994,35</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-66,95; 992,08</t>
+          <t>-76,51; 1030,17</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
@@ -798,7 +798,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-73,26; 576,38</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -813,17 +813,17 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,83; 585,49</t>
+          <t>20,81; 613,11</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-56,14; 388,7</t>
+          <t>-57,65; 279,84</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-95,82; 419,58</t>
+          <t>-65,76; 529,4</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3,99</t>
+          <t>3,81</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-0,34</t>
+          <t>-0,38</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>2,37</t>
+          <t>2,25</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,96; 4,63</t>
+          <t>0,94; 4,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,25; 5,2</t>
+          <t>1,27; 4,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,86; 9,71</t>
+          <t>1,1; 8,82</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,15</t>
+          <t>-2,31; 1,19</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-0,79; 3,39</t>
+          <t>-1,02; 3,43</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-1,91; 1,81</t>
+          <t>-1,89; 1,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 3,15</t>
+          <t>0,39; 3,04</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,84; 3,74</t>
+          <t>0,9; 3,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 5,5</t>
+          <t>0,42; 5,34</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>710,7%</t>
+          <t>679,76%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-36,0%</t>
+          <t>-40,23%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>349,79%</t>
+          <t>332,72%</t>
         </is>
       </c>
     </row>
@@ -999,17 +999,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,52; 2471,53</t>
+          <t>46,05; 2156,58</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>51,51; 2336,04</t>
+          <t>48,26; 2293,01</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-23,96; —</t>
+          <t>6,71; 3930,87</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1019,7 +1019,7 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-84,1; —</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1029,17 +1029,17 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,5; 1163,86</t>
+          <t>16,45; 994,09</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>48,69; 1390,2</t>
+          <t>61,37; 1307,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 1475,99</t>
+          <t>7,23; 1524,69</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,47</t>
+          <t>1,01</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,85</t>
+          <t>0,78</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>0,6</t>
+          <t>0,93</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,91; 4,37</t>
+          <t>0,91; 4,44</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>0,17; 3,03</t>
+          <t>0,22; 2,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,24</t>
+          <t>-0,2; 3,08</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-1,45; 0,78</t>
+          <t>-1,46; 0,78</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-1,34; 1,47</t>
+          <t>-1,05; 1,47</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,55; 2,99</t>
+          <t>-0,62; 2,7</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>0,48; 2,93</t>
+          <t>0,48; 2,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-0,04; 2,02</t>
+          <t>-0,03; 2,06</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-0,26; 1,75</t>
+          <t>-0,05; 2,36</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103,04%</t>
+          <t>220,15%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>186,61%</t>
+          <t>171,97%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>131,91%</t>
+          <t>203,37%</t>
         </is>
       </c>
     </row>
@@ -1215,12 +1215,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>11,64; —</t>
+          <t>12,85; —</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>-43,72; —</t>
+          <t>-42,37; —</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -1245,17 +1245,17 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 1636,54</t>
+          <t>25,14; 1725,35</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>-33,08; 1190,11</t>
+          <t>-31,22; 1750,09</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-68,31; —</t>
+          <t>-44,35; —</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1,19</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,4</t>
+          <t>0,76</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>0,94</t>
+          <t>1,2</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,54; 3,18</t>
+          <t>0,55; 3,33</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,95; 4,47</t>
+          <t>0,99; 4,68</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,3; 2,82</t>
+          <t>0,52; 3,2</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-4,0; 0,0</t>
+          <t>-4,05; 0,0</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-2,38; 1,68</t>
+          <t>-2,77; 1,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-2,24; 1,85</t>
+          <t>-1,83; 2,35</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-0,18; 1,81</t>
+          <t>-0,09; 1,79</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>0,39; 2,97</t>
+          <t>0,38; 2,94</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-0,05; 1,97</t>
+          <t>0,24; 2,27</t>
         </is>
       </c>
     </row>
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>49,52%</t>
+          <t>93,73%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>367,37%</t>
+          <t>470,31%</t>
         </is>
       </c>
     </row>
@@ -1498,7 +1498,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>0,04</t>
+          <t>-0,25</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,26</t>
+          <t>1,21</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>0,36</t>
+          <t>0,15</t>
         </is>
       </c>
     </row>
@@ -1541,47 +1541,47 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-5,09; 1,77</t>
+          <t>-5,53; 1,6</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-5,66; 1,03</t>
+          <t>-5,37; 1,32</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-3,93; 3,07</t>
+          <t>-3,98; 3,06</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-8,14; 0,0</t>
+          <t>-6,93; 0,0</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-6,26; 0,0</t>
+          <t>-6,9; 0,0</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-3,57; 3,79</t>
+          <t>-3,28; 3,9</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>-4,67; 0,69</t>
+          <t>-4,76; 0,62</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>-4,77; 0,55</t>
+          <t>-4,43; 0,41</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>-2,87; 2,63</t>
+          <t>-3,08; 2,28</t>
         </is>
       </c>
     </row>
@@ -1604,7 +1604,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>-7,17%</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -1619,7 +1619,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,55%</t>
+          <t>88,71%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -1634,7 +1634,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-100,0; 218,46</t>
+          <t>-100,0; 238,72</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-93,42; 116,16</t>
+          <t>-90,84; 133,02</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-66,55; 191,17</t>
+          <t>-68,45; 235,57</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -1677,17 +1677,17 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>-97,43; 80,38</t>
+          <t>-100,0; 109,81</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>-94,89; 65,38</t>
+          <t>-91,44; 66,4</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>-58,58; 194,86</t>
+          <t>-63,09; 164,06</t>
         </is>
       </c>
     </row>
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>1,33</t>
+          <t>1,59</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -1729,7 +1729,7 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,16</t>
+          <t>0,57</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
@@ -1744,7 +1744,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>1,31</t>
         </is>
       </c>
     </row>
@@ -1757,17 +1757,17 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>0,63; 7,66</t>
+          <t>0,63; 7,7</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,74</t>
+          <t>0,0; 2,95</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>0,36; 3,17</t>
+          <t>0,53; 3,55</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -1782,22 +1782,22 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 1,22</t>
+          <t>0,0; 3,44</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>0,47; 6,18</t>
+          <t>0,46; 5,82</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
         <is>
-          <t>0,0; 2,49</t>
+          <t>0,0; 2,19</t>
         </is>
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,61</t>
+          <t>0,52; 2,96</t>
         </is>
       </c>
     </row>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>0,44</t>
+          <t>0,37</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -1945,7 +1945,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,52</t>
+          <t>1,43</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -1960,7 +1960,7 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>0,63</t>
+          <t>0,55</t>
         </is>
       </c>
     </row>
@@ -1973,17 +1973,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>-2,72; 10,41</t>
+          <t>-2,76; 10,62</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>-5,45; 1,71</t>
+          <t>-4,84; 1,69</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>-4,45; 2,98</t>
+          <t>-4,3; 3,06</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -1998,22 +1998,22 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,6</t>
+          <t>0,0; 7,45</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>-2,27; 8,24</t>
+          <t>-2,22; 8,18</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
         <is>
-          <t>-4,48; 1,22</t>
+          <t>-4,86; 1,21</t>
         </is>
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>-3,04; 2,94</t>
+          <t>-3,1; 2,81</t>
         </is>
       </c>
     </row>
@@ -2036,7 +2036,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>26,75%</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -2066,7 +2066,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>56,15%</t>
+          <t>49,38%</t>
         </is>
       </c>
     </row>
@@ -2146,7 +2146,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>1,15</t>
+          <t>1,35</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>0,28</t>
+          <t>0,85</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>0,82</t>
+          <t>1,18</t>
         </is>
       </c>
     </row>
@@ -2189,47 +2189,47 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>1,2; 3,04</t>
+          <t>1,21; 3,07</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>0,51; 2,12</t>
+          <t>0,59; 2,14</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>0,33; 2,17</t>
+          <t>0,58; 2,37</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 0,44</t>
+          <t>-1,33; 0,43</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 0,86</t>
+          <t>-0,9; 0,86</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>-0,82; 1,36</t>
+          <t>-0,21; 2,18</t>
         </is>
       </c>
       <c r="I33" s="2" t="inlineStr">
         <is>
-          <t>0,59; 1,88</t>
+          <t>0,54; 1,89</t>
         </is>
       </c>
       <c r="J33" s="2" t="inlineStr">
         <is>
-          <t>0,23; 1,42</t>
+          <t>0,29; 1,4</t>
         </is>
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>0,08; 1,54</t>
+          <t>0,54; 2,02</t>
         </is>
       </c>
     </row>
@@ -2252,7 +2252,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>140,34%</t>
+          <t>165,45%</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -2267,7 +2267,7 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>26,39%</t>
+          <t>81,69%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
@@ -2282,7 +2282,7 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>132,93%</t>
         </is>
       </c>
     </row>
@@ -2295,47 +2295,47 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>92,96; 543,63</t>
+          <t>101,96; 595,01</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>38,4; 393,79</t>
+          <t>50,35; 435,98</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>20,03; 366,01</t>
+          <t>37,56; 446,91</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-78,24; 100,15</t>
+          <t>-79,42; 105,04</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-61,33; 169,78</t>
+          <t>-59,05; 180,05</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>-52,38; 214,67</t>
+          <t>-21,99; 358,46</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>48,87; 288,83</t>
+          <t>38,84; 276,78</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
         <is>
-          <t>16,6; 224,96</t>
+          <t>20,33; 213,81</t>
         </is>
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>5,96; 229,3</t>
+          <t>43,76; 311,91</t>
         </is>
       </c>
     </row>
